--- a/data/labour-market/Education, employment and NEET outcomes among (aged 16–24)/NEET rates among 16–24 year olds by English region, 2025.xlsx
+++ b/data/labour-market/Education, employment and NEET outcomes among (aged 16–24)/NEET rates among 16–24 year olds by English region, 2025.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analysis_data" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw_data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observations" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3544,6 +3545,1882 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AJ12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="40" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="28" max="28"/>
+    <col width="22" customWidth="1" min="29" max="29"/>
+    <col width="42" customWidth="1" min="30" max="30"/>
+    <col width="33" customWidth="1" min="31" max="31"/>
+    <col width="57" customWidth="1" min="32" max="32"/>
+    <col width="38" customWidth="1" min="33" max="33"/>
+    <col width="60" customWidth="1" min="34" max="34"/>
+    <col width="20" customWidth="1" min="35" max="35"/>
+    <col width="14" customWidth="1" min="36" max="36"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Dataset_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Indicator_Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Public_Source_Title</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Public_Source_URL</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Period_Type</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Reference_Year</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Source_Geography</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Source_Geography_Code</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Final_Geography</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Final_Geography_Code</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Geography_Type</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Measure_ID</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Measure_Label</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Numerator</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Denominator</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Denominator_Label</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Percentage</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Lower_CI_95</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Upper_CI_95</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Confidence_Interval</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Age_Group</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Category_Type</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Dimensions_JSON</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Source_Table</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Source_Row_Label</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Source_Column_Label</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Aggregation_Flag</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Calculation_Notes</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Data_Quality_Notes</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Last_Updated</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>dfe_ees_neet_lfs</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>NEET rates among 16–24 year olds by English region, 2025</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>NEET and NET Estimates from the LFS</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>https://explore-education-statistics.service.gov.uk/find-statistics/neet-statistics-annual-brief</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>survey_period</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>North East</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>E12000001</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>North East</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>E12000001</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>neet_rate_16_24</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>NEET rate, aged 16-24</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>246748</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>1212351</v>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>Population aged 16-24 (LFS yearly sum)</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>246748</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr"/>
+      <c r="W2" s="2" t="inlineStr"/>
+      <c r="X2" s="2" t="inlineStr"/>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>16-24</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>NEET</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>Labour market status</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>{"category": "NEET"}</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>EES: NEET and NET Estimates from the LFS</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>North East - 2025</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>IND_NEET_PCT/IND_NUM_NEET/IND_POP (yearly sum of Q1-Q4)</t>
+        </is>
+      </c>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
+          <t>Calculated aggregate</t>
+        </is>
+      </c>
+      <c r="AH2" s="2" t="inlineStr">
+        <is>
+          <t>Yearly average: sum(Number NEET Q1–Q4) / sum(Population Q1–Q4) × 100</t>
+        </is>
+      </c>
+      <c r="AI2" s="2" t="inlineStr"/>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>dfe_ees_neet_lfs</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>NEET rates among 16–24 year olds by English region, 2025</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>NEET and NET Estimates from the LFS</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>https://explore-education-statistics.service.gov.uk/find-statistics/neet-statistics-annual-brief</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>survey_period</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>North West</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>E12000002</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>North West</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>E12000002</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>neet_rate_16_24</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>NEET rate, aged 16-24</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>502303</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>3411495</v>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>Population aged 16-24 (LFS yearly sum)</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>502303</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr"/>
+      <c r="W3" s="2" t="inlineStr"/>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t>16-24</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
+          <t>NEET</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>Labour market status</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>{"category": "NEET"}</t>
+        </is>
+      </c>
+      <c r="AD3" s="2" t="inlineStr">
+        <is>
+          <t>EES: NEET and NET Estimates from the LFS</t>
+        </is>
+      </c>
+      <c r="AE3" s="2" t="inlineStr">
+        <is>
+          <t>North West - 2025</t>
+        </is>
+      </c>
+      <c r="AF3" s="2" t="inlineStr">
+        <is>
+          <t>IND_NEET_PCT/IND_NUM_NEET/IND_POP (yearly sum of Q1-Q4)</t>
+        </is>
+      </c>
+      <c r="AG3" s="2" t="inlineStr">
+        <is>
+          <t>Calculated aggregate</t>
+        </is>
+      </c>
+      <c r="AH3" s="2" t="inlineStr">
+        <is>
+          <t>Yearly average: sum(Number NEET Q1–Q4) / sum(Population Q1–Q4) × 100</t>
+        </is>
+      </c>
+      <c r="AI3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>dfe_ees_neet_lfs</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>NEET rates among 16–24 year olds by English region, 2025</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>NEET and NET Estimates from the LFS</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>https://explore-education-statistics.service.gov.uk/find-statistics/neet-statistics-annual-brief</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>survey_period</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Yorkshire and The Humber</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>E12000003</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Yorkshire and The Humber</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>E12000003</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>neet_rate_16_24</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>NEET rate, aged 16-24</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>429629</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>2535889</v>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>Population aged 16-24 (LFS yearly sum)</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>429629</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr"/>
+      <c r="W4" s="2" t="inlineStr"/>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t>16-24</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
+          <t>NEET</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>Labour market status</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>{"category": "NEET"}</t>
+        </is>
+      </c>
+      <c r="AD4" s="2" t="inlineStr">
+        <is>
+          <t>EES: NEET and NET Estimates from the LFS</t>
+        </is>
+      </c>
+      <c r="AE4" s="2" t="inlineStr">
+        <is>
+          <t>Yorkshire and The Humber - 2025</t>
+        </is>
+      </c>
+      <c r="AF4" s="2" t="inlineStr">
+        <is>
+          <t>IND_NEET_PCT/IND_NUM_NEET/IND_POP (yearly sum of Q1-Q4)</t>
+        </is>
+      </c>
+      <c r="AG4" s="2" t="inlineStr">
+        <is>
+          <t>Calculated aggregate</t>
+        </is>
+      </c>
+      <c r="AH4" s="2" t="inlineStr">
+        <is>
+          <t>Yearly average: sum(Number NEET Q1–Q4) / sum(Population Q1–Q4) × 100</t>
+        </is>
+      </c>
+      <c r="AI4" s="2" t="inlineStr"/>
+      <c r="AJ4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>dfe_ees_neet_lfs</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>NEET rates among 16–24 year olds by English region, 2025</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>NEET and NET Estimates from the LFS</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>https://explore-education-statistics.service.gov.uk/find-statistics/neet-statistics-annual-brief</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>survey_period</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>East Midlands</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>E12000004</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>East Midlands</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>E12000004</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>neet_rate_16_24</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>NEET rate, aged 16-24</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>374624</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>2212400</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>Population aged 16-24 (LFS yearly sum)</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>374624</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr"/>
+      <c r="Y5" s="2" t="inlineStr"/>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>16-24</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>NEET</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>Labour market status</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>{"category": "NEET"}</t>
+        </is>
+      </c>
+      <c r="AD5" s="2" t="inlineStr">
+        <is>
+          <t>EES: NEET and NET Estimates from the LFS</t>
+        </is>
+      </c>
+      <c r="AE5" s="2" t="inlineStr">
+        <is>
+          <t>East Midlands - 2025</t>
+        </is>
+      </c>
+      <c r="AF5" s="2" t="inlineStr">
+        <is>
+          <t>IND_NEET_PCT/IND_NUM_NEET/IND_POP (yearly sum of Q1-Q4)</t>
+        </is>
+      </c>
+      <c r="AG5" s="2" t="inlineStr">
+        <is>
+          <t>Calculated aggregate</t>
+        </is>
+      </c>
+      <c r="AH5" s="2" t="inlineStr">
+        <is>
+          <t>Yearly average: sum(Number NEET Q1–Q4) / sum(Population Q1–Q4) × 100</t>
+        </is>
+      </c>
+      <c r="AI5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>dfe_ees_neet_lfs</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>NEET rates among 16–24 year olds by English region, 2025</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>NEET and NET Estimates from the LFS</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>https://explore-education-statistics.service.gov.uk/find-statistics/neet-statistics-annual-brief</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>survey_period</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>West Midlands</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>E12000005</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>West Midlands</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>E12000005</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>neet_rate_16_24</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>NEET rate, aged 16-24</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>347427</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>2698994</v>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>Population aged 16-24 (LFS yearly sum)</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>347427</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr"/>
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>16-24</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>NEET</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>Labour market status</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>{"category": "NEET"}</t>
+        </is>
+      </c>
+      <c r="AD6" s="2" t="inlineStr">
+        <is>
+          <t>EES: NEET and NET Estimates from the LFS</t>
+        </is>
+      </c>
+      <c r="AE6" s="2" t="inlineStr">
+        <is>
+          <t>West Midlands - 2025</t>
+        </is>
+      </c>
+      <c r="AF6" s="2" t="inlineStr">
+        <is>
+          <t>IND_NEET_PCT/IND_NUM_NEET/IND_POP (yearly sum of Q1-Q4)</t>
+        </is>
+      </c>
+      <c r="AG6" s="2" t="inlineStr">
+        <is>
+          <t>Calculated aggregate</t>
+        </is>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>Yearly average: sum(Number NEET Q1–Q4) / sum(Population Q1–Q4) × 100</t>
+        </is>
+      </c>
+      <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>dfe_ees_neet_lfs</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>NEET rates among 16–24 year olds by English region, 2025</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>NEET and NET Estimates from the LFS</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>https://explore-education-statistics.service.gov.uk/find-statistics/neet-statistics-annual-brief</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>survey_period</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>East of England</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>E12000006</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>East of England</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>E12000006</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>neet_rate_16_24</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>NEET rate, aged 16-24</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>276743</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>2493748</v>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>Population aged 16-24 (LFS yearly sum)</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>276743</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr"/>
+      <c r="W7" s="2" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>16-24</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>NEET</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>Labour market status</t>
+        </is>
+      </c>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>{"category": "NEET"}</t>
+        </is>
+      </c>
+      <c r="AD7" s="2" t="inlineStr">
+        <is>
+          <t>EES: NEET and NET Estimates from the LFS</t>
+        </is>
+      </c>
+      <c r="AE7" s="2" t="inlineStr">
+        <is>
+          <t>East of England - 2025</t>
+        </is>
+      </c>
+      <c r="AF7" s="2" t="inlineStr">
+        <is>
+          <t>IND_NEET_PCT/IND_NUM_NEET/IND_POP (yearly sum of Q1-Q4)</t>
+        </is>
+      </c>
+      <c r="AG7" s="2" t="inlineStr">
+        <is>
+          <t>Calculated aggregate</t>
+        </is>
+      </c>
+      <c r="AH7" s="2" t="inlineStr">
+        <is>
+          <t>Yearly average: sum(Number NEET Q1–Q4) / sum(Population Q1–Q4) × 100</t>
+        </is>
+      </c>
+      <c r="AI7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>dfe_ees_neet_lfs</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>NEET rates among 16–24 year olds by English region, 2025</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>NEET and NET Estimates from the LFS</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>https://explore-education-statistics.service.gov.uk/find-statistics/neet-statistics-annual-brief</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>survey_period</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>E12000007</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>E12000007</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>neet_rate_16_24</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>NEET rate, aged 16-24</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>544068</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>4181652</v>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>Population aged 16-24 (LFS yearly sum)</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>544068</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr"/>
+      <c r="W8" s="2" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>16-24</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>NEET</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>Labour market status</t>
+        </is>
+      </c>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>{"category": "NEET"}</t>
+        </is>
+      </c>
+      <c r="AD8" s="2" t="inlineStr">
+        <is>
+          <t>EES: NEET and NET Estimates from the LFS</t>
+        </is>
+      </c>
+      <c r="AE8" s="2" t="inlineStr">
+        <is>
+          <t>London - 2025</t>
+        </is>
+      </c>
+      <c r="AF8" s="2" t="inlineStr">
+        <is>
+          <t>IND_NEET_PCT/IND_NUM_NEET/IND_POP (yearly sum of Q1-Q4)</t>
+        </is>
+      </c>
+      <c r="AG8" s="2" t="inlineStr">
+        <is>
+          <t>Calculated aggregate</t>
+        </is>
+      </c>
+      <c r="AH8" s="2" t="inlineStr">
+        <is>
+          <t>Yearly average: sum(Number NEET Q1–Q4) / sum(Population Q1–Q4) × 100</t>
+        </is>
+      </c>
+      <c r="AI8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>dfe_ees_neet_lfs</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>NEET rates among 16–24 year olds by English region, 2025</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>NEET and NET Estimates from the LFS</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>https://explore-education-statistics.service.gov.uk/find-statistics/neet-statistics-annual-brief</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>survey_period</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>South East</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>E12000008</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>South East</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>E12000008</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>neet_rate_16_24</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>NEET rate, aged 16-24</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>408308</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>3790106</v>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>Population aged 16-24 (LFS yearly sum)</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>408308</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr"/>
+      <c r="W9" s="2" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr"/>
+      <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>16-24</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>NEET</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>Labour market status</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>{"category": "NEET"}</t>
+        </is>
+      </c>
+      <c r="AD9" s="2" t="inlineStr">
+        <is>
+          <t>EES: NEET and NET Estimates from the LFS</t>
+        </is>
+      </c>
+      <c r="AE9" s="2" t="inlineStr">
+        <is>
+          <t>South East - 2025</t>
+        </is>
+      </c>
+      <c r="AF9" s="2" t="inlineStr">
+        <is>
+          <t>IND_NEET_PCT/IND_NUM_NEET/IND_POP (yearly sum of Q1-Q4)</t>
+        </is>
+      </c>
+      <c r="AG9" s="2" t="inlineStr">
+        <is>
+          <t>Calculated aggregate</t>
+        </is>
+      </c>
+      <c r="AH9" s="2" t="inlineStr">
+        <is>
+          <t>Yearly average: sum(Number NEET Q1–Q4) / sum(Population Q1–Q4) × 100</t>
+        </is>
+      </c>
+      <c r="AI9" s="2" t="inlineStr"/>
+      <c r="AJ9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>dfe_ees_neet_lfs</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>NEET rates among 16–24 year olds by English region, 2025</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>NEET and NET Estimates from the LFS</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>https://explore-education-statistics.service.gov.uk/find-statistics/neet-statistics-annual-brief</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>survey_period</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>South West</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>E12000009</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>South West</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>E12000009</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>neet_rate_16_24</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>NEET rate, aged 16-24</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>243117</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>2364539</v>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>Population aged 16-24 (LFS yearly sum)</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>243117</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr"/>
+      <c r="W10" s="2" t="inlineStr"/>
+      <c r="X10" s="2" t="inlineStr"/>
+      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>16-24</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>NEET</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>Labour market status</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>{"category": "NEET"}</t>
+        </is>
+      </c>
+      <c r="AD10" s="2" t="inlineStr">
+        <is>
+          <t>EES: NEET and NET Estimates from the LFS</t>
+        </is>
+      </c>
+      <c r="AE10" s="2" t="inlineStr">
+        <is>
+          <t>South West - 2025</t>
+        </is>
+      </c>
+      <c r="AF10" s="2" t="inlineStr">
+        <is>
+          <t>IND_NEET_PCT/IND_NUM_NEET/IND_POP (yearly sum of Q1-Q4)</t>
+        </is>
+      </c>
+      <c r="AG10" s="2" t="inlineStr">
+        <is>
+          <t>Calculated aggregate</t>
+        </is>
+      </c>
+      <c r="AH10" s="2" t="inlineStr">
+        <is>
+          <t>Yearly average: sum(Number NEET Q1–Q4) / sum(Population Q1–Q4) × 100</t>
+        </is>
+      </c>
+      <c r="AI10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>dfe_ees_neet_lfs</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>NEET rates among 16–24 year olds by English region, 2025</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>NEET and NET Estimates from the LFS</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>https://explore-education-statistics.service.gov.uk/find-statistics/neet-statistics-annual-brief</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>survey_period</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>E92000001</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>E92000001</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>neet_rate_16_24</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>NEET rate, aged 16-24</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>3372966</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>24901173</v>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>Population aged 16-24 (LFS yearly sum)</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="n">
+        <v>3372966</v>
+      </c>
+      <c r="U11" s="2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr"/>
+      <c r="W11" s="2" t="inlineStr"/>
+      <c r="X11" s="2" t="inlineStr"/>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>16-24</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>NEET</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>Labour market status</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>{"category": "NEET"}</t>
+        </is>
+      </c>
+      <c r="AD11" s="2" t="inlineStr">
+        <is>
+          <t>EES: NEET and NET Estimates from the LFS</t>
+        </is>
+      </c>
+      <c r="AE11" s="2" t="inlineStr">
+        <is>
+          <t>England - 2025</t>
+        </is>
+      </c>
+      <c r="AF11" s="2" t="inlineStr">
+        <is>
+          <t>IND_NEET_PCT/IND_NUM_NEET/IND_POP (yearly sum of Q1-Q4)</t>
+        </is>
+      </c>
+      <c r="AG11" s="2" t="inlineStr">
+        <is>
+          <t>Calculated aggregate</t>
+        </is>
+      </c>
+      <c r="AH11" s="2" t="inlineStr">
+        <is>
+          <t>Yearly average: sum(Number NEET Q1–Q4) / sum(Population Q1–Q4) × 100</t>
+        </is>
+      </c>
+      <c r="AI11" s="2" t="inlineStr"/>
+      <c r="AJ11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>dfe_ees_neet_lfs</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>NEET rates among 16–24 year olds by English region, 2025</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>NEET and NET Estimates from the LFS</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>https://explore-education-statistics.service.gov.uk/find-statistics/neet-statistics-annual-brief</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>survey_period</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>England excluding London</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>England excluding London</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>custom_aggregate</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>neet_rate_16_24</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>NEET rate, aged 16-24</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>2828899</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>20719521</v>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>Population aged 16-24 (LFS yearly sum)</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>2828899</v>
+      </c>
+      <c r="U12" s="2" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr"/>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>16-24</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>NEET</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>Labour market status</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>{"category": "NEET"}</t>
+        </is>
+      </c>
+      <c r="AD12" s="2" t="inlineStr">
+        <is>
+          <t>EES: NEET and NET Estimates from the LFS</t>
+        </is>
+      </c>
+      <c r="AE12" s="2" t="inlineStr">
+        <is>
+          <t>England excluding London - 2025</t>
+        </is>
+      </c>
+      <c r="AF12" s="2" t="inlineStr">
+        <is>
+          <t>IND_NEET_PCT/IND_NUM_NEET/IND_POP (yearly sum of Q1-Q4)</t>
+        </is>
+      </c>
+      <c r="AG12" s="2" t="inlineStr">
+        <is>
+          <t>England excluding London calculation</t>
+        </is>
+      </c>
+      <c r="AH12" s="2" t="inlineStr">
+        <is>
+          <t>Yearly average: (sum(England NEET Q1–Q4) − sum(London NEET Q1–Q4)) / (sum(England pop Q1–Q4) − sum(London pop Q1–Q4)) × 100</t>
+        </is>
+      </c>
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3643,7 +5520,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>

--- a/data/labour-market/Education, employment and NEET outcomes among (aged 16–24)/NEET rates among 16–24 year olds by English region, 2025.xlsx
+++ b/data/labour-market/Education, employment and NEET outcomes among (aged 16–24)/NEET rates among 16–24 year olds by English region, 2025.xlsx
@@ -3914,7 +3914,7 @@
       <c r="AI2" s="2" t="inlineStr"/>
       <c r="AJ2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
       <c r="AI3" s="2" t="inlineStr"/>
       <c r="AJ3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       <c r="AI4" s="2" t="inlineStr"/>
       <c r="AJ4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       <c r="AI5" s="2" t="inlineStr"/>
       <c r="AJ5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       <c r="AI6" s="2" t="inlineStr"/>
       <c r="AJ6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
       <c r="AI7" s="2" t="inlineStr"/>
       <c r="AJ7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       <c r="AI8" s="2" t="inlineStr"/>
       <c r="AJ8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -4964,7 +4964,7 @@
       <c r="AI9" s="2" t="inlineStr"/>
       <c r="AJ9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5114,7 @@
       <c r="AI10" s="2" t="inlineStr"/>
       <c r="AJ10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
       <c r="AI11" s="2" t="inlineStr"/>
       <c r="AJ11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       <c r="AI12" s="2" t="inlineStr"/>
       <c r="AJ12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
